--- a/tiflow-xborder/build/0.9.0/StructureDefinition-GEM-ERPEU-PR-Organization.xlsx
+++ b/tiflow-xborder/build/0.9.0/StructureDefinition-GEM-ERPEU-PR-Organization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2296" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2292" uniqueCount="505">
   <si>
     <t>Property</t>
   </si>
@@ -436,7 +436,7 @@
     <t>Organization.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -474,7 +474,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -508,7 +508,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -551,7 +551,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -826,15 +826,7 @@
     <t>Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
-    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
-Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
-  </si>
-  <si>
     <t>Identifier.period</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
   </si>
   <si>
     <t>CX.7 + CX.8</t>
@@ -865,10 +857,6 @@
     <t>Identifier.assigner</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
-  </si>
-  <si>
     <t>CX.4 / (CX.4,CX.9,CX.10)</t>
   </si>
   <si>
@@ -888,10 +876,10 @@
 </t>
   </si>
   <si>
-    <t>An identifier intended for computation</t>
-  </si>
-  <si>
-    <t>An identifier - identifies some entity uniquely and unambiguously. Typically this is used for business identifiers.</t>
+    <t>Identifies this organization  across multiple systems</t>
+  </si>
+  <si>
+    <t>Identifier for the organization that is used to identify the organization across multiple disparate systems.</t>
   </si>
   <si>
     <t>Organization.identifier:BSNR</t>
@@ -979,7 +967,7 @@
     <t>Used to categorize the organization.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/organization-type</t>
+    <t>http://hl7.org/fhir/ValueSet/organization-type|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">pattern:$this}
@@ -1389,6 +1377,10 @@
   </si>
   <si>
     <t>Time period when address was/is in use.</t>
+  </si>
+  <si>
+    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
+Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
   </si>
   <si>
     <t>Allows addresses to be placed in historical context.</t>
@@ -1403,6 +1395,10 @@
     <t>Address.period</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
+  </si>
+  <si>
     <t>XAD.12 / XAD.13 + XAD.14</t>
   </si>
   <si>
@@ -1412,10 +1408,6 @@
     <t>Organization.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
-</t>
-  </si>
-  <si>
     <t>The organization of which this organization forms a part</t>
   </si>
   <si>
@@ -1426,6 +1418,10 @@
   </si>
   <si>
     <t>Need to be able to track the hierarchy of organizations within an organization.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
   </si>
   <si>
     <t>.playedBy[classCode=Part].scoper</t>
@@ -1494,7 +1490,7 @@
     <t>The purpose for which you would contact a contact party.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/contactentity-type</t>
+    <t>http://hl7.org/fhir/ValueSet/contactentity-type|4.0.1</t>
   </si>
   <si>
     <t>CE/CNE/CWE</t>
@@ -1583,7 +1579,7 @@
     <t>Organization.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint)
+    <t xml:space="preserve">Reference(Endpoint|4.0.1)
 </t>
   </si>
   <si>
@@ -3908,7 +3904,7 @@
         <v>194</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3935,9 +3931,7 @@
       <c r="M18" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="N18" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>77</v>
@@ -3995,7 +3989,7 @@
         <v>79</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>116</v>
@@ -4004,7 +3998,7 @@
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -4683,7 +4677,7 @@
         <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>99</v>
@@ -4967,9 +4961,7 @@
       <c r="M27" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="N27" t="s" s="2">
-        <v>260</v>
-      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -5018,7 +5010,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -5027,19 +5019,19 @@
         <v>87</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="AJ27" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK27" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AL27" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="AK27" t="s" s="2">
+      <c r="AM27" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>77</v>
@@ -5047,10 +5039,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5073,16 +5065,16 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5132,7 +5124,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5141,19 +5133,19 @@
         <v>87</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="AJ28" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="AK28" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>77</v>
@@ -5161,13 +5153,13 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>203</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>77</v>
@@ -5189,13 +5181,13 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
@@ -5277,13 +5269,13 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>203</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>77</v>
@@ -5305,13 +5297,13 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
@@ -5393,13 +5385,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>203</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>77</v>
@@ -5421,13 +5413,13 @@
         <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
@@ -5509,13 +5501,13 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>203</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>77</v>
@@ -5537,13 +5529,13 @@
         <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
@@ -5625,10 +5617,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5651,26 +5643,26 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="N33" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="P33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q33" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="N33" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="P33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q33" t="s" s="2">
-        <v>296</v>
-      </c>
       <c r="R33" t="s" s="2">
         <v>77</v>
       </c>
@@ -5714,7 +5706,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5729,24 +5721,24 @@
         <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>300</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5772,16 +5764,16 @@
         <v>228</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="O34" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5809,16 +5801,16 @@
         <v>156</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="AC34" s="2"/>
       <c r="AD34" t="s" s="2">
@@ -5828,7 +5820,7 @@
         <v>114</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5843,27 +5835,27 @@
         <v>99</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>77</v>
@@ -5888,16 +5880,16 @@
         <v>228</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="O35" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5924,11 +5916,9 @@
       <c r="X35" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="Y35" t="s" s="2">
-        <v>306</v>
-      </c>
+      <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>77</v>
@@ -5946,7 +5936,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5961,27 +5951,27 @@
         <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>77</v>
@@ -6006,16 +5996,16 @@
         <v>228</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="O36" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -6042,11 +6032,9 @@
       <c r="X36" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="Y36" t="s" s="2">
-        <v>306</v>
-      </c>
+      <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>77</v>
@@ -6064,7 +6052,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6079,24 +6067,24 @@
         <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6122,16 +6110,16 @@
         <v>101</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="O37" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -6180,7 +6168,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6189,19 +6177,19 @@
         <v>87</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>77</v>
@@ -6209,10 +6197,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6238,16 +6226,16 @@
         <v>101</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="O38" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>77</v>
@@ -6296,7 +6284,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6314,7 +6302,7 @@
         <v>77</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>77</v>
@@ -6325,10 +6313,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6351,19 +6339,19 @@
         <v>77</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="N39" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -6412,7 +6400,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6421,19 +6409,19 @@
         <v>79</v>
       </c>
       <c r="AI39" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AL39" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="AJ39" t="s" s="2">
+      <c r="AM39" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="AK39" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>77</v>
@@ -6441,10 +6429,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6467,19 +6455,19 @@
         <v>77</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="N40" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>77</v>
@@ -6528,7 +6516,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6537,19 +6525,19 @@
         <v>79</v>
       </c>
       <c r="AI40" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AL40" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AJ40" t="s" s="2">
+      <c r="AM40" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="AK40" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>77</v>
@@ -6557,10 +6545,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6669,10 +6657,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6783,10 +6771,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6812,16 +6800,16 @@
         <v>166</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="O43" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -6834,7 +6822,7 @@
         <v>77</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="U43" t="s" s="2">
         <v>77</v>
@@ -6849,10 +6837,10 @@
         <v>222</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>77</v>
@@ -6870,7 +6858,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6885,13 +6873,13 @@
         <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>77</v>
@@ -6899,10 +6887,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6928,13 +6916,13 @@
         <v>166</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6948,7 +6936,7 @@
         <v>77</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>77</v>
@@ -6963,10 +6951,10 @@
         <v>222</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>77</v>
@@ -6984,7 +6972,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6999,10 +6987,10 @@
         <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
@@ -7013,10 +7001,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7042,16 +7030,16 @@
         <v>101</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="O45" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -7064,7 +7052,7 @@
         <v>77</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="U45" t="s" s="2">
         <v>77</v>
@@ -7100,7 +7088,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7115,10 +7103,10 @@
         <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
@@ -7129,10 +7117,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7158,13 +7146,13 @@
         <v>101</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7178,7 +7166,7 @@
         <v>77</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>77</v>
@@ -7214,7 +7202,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7229,13 +7217,13 @@
         <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>77</v>
@@ -7243,14 +7231,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7272,13 +7260,13 @@
         <v>101</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7292,7 +7280,7 @@
         <v>77</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>77</v>
@@ -7328,7 +7316,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7343,13 +7331,13 @@
         <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>77</v>
@@ -7357,14 +7345,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7386,13 +7374,13 @@
         <v>101</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7406,7 +7394,7 @@
         <v>77</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="U48" t="s" s="2">
         <v>77</v>
@@ -7442,7 +7430,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7457,10 +7445,10 @@
         <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>77</v>
@@ -7471,14 +7459,14 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7500,13 +7488,13 @@
         <v>101</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7556,7 +7544,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7571,13 +7559,13 @@
         <v>99</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>77</v>
@@ -7585,14 +7573,14 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7614,13 +7602,13 @@
         <v>101</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7634,7 +7622,7 @@
         <v>77</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="U50" t="s" s="2">
         <v>77</v>
@@ -7670,7 +7658,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7685,13 +7673,13 @@
         <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>77</v>
@@ -7699,10 +7687,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7728,13 +7716,13 @@
         <v>101</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7784,7 +7772,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7799,13 +7787,13 @@
         <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>77</v>
@@ -7813,10 +7801,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7842,16 +7830,16 @@
         <v>257</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="O52" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -7864,7 +7852,7 @@
         <v>77</v>
       </c>
       <c r="T52" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="U52" t="s" s="2">
         <v>77</v>
@@ -7900,7 +7888,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7912,16 +7900,16 @@
         <v>149</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>262</v>
+        <v>441</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AL52" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="AL52" t="s" s="2">
-        <v>444</v>
-      </c>
       <c r="AM52" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>77</v>
@@ -7929,10 +7917,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7955,19 +7943,19 @@
         <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>77</v>
@@ -8016,7 +8004,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8028,13 +8016,13 @@
         <v>149</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>272</v>
+        <v>449</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>105</v>
@@ -8045,10 +8033,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8071,19 +8059,19 @@
         <v>77</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="N54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -8132,7 +8120,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8150,7 +8138,7 @@
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
@@ -8161,10 +8149,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8273,10 +8261,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8387,14 +8375,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8416,10 +8404,10 @@
         <v>108</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>111</v>
@@ -8474,7 +8462,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8503,10 +8491,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8532,16 +8520,16 @@
         <v>228</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="N58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>77</v>
@@ -8569,11 +8557,11 @@
         <v>145</v>
       </c>
       <c r="Y58" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="Z58" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="Z58" t="s" s="2">
-        <v>472</v>
-      </c>
       <c r="AA58" t="s" s="2">
         <v>77</v>
       </c>
@@ -8590,7 +8578,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8605,10 +8593,10 @@
         <v>99</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AL58" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>77</v>
@@ -8619,10 +8607,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8645,19 +8633,19 @@
         <v>77</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="N59" t="s" s="2">
+      <c r="O59" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -8706,7 +8694,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8721,13 +8709,13 @@
         <v>99</v>
       </c>
       <c r="AK59" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AL59" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="AL59" t="s" s="2">
+      <c r="AM59" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>483</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>77</v>
@@ -8735,10 +8723,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8761,17 +8749,17 @@
         <v>77</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>486</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>77</v>
@@ -8820,7 +8808,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8832,16 +8820,16 @@
         <v>149</v>
       </c>
       <c r="AJ60" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AK60" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="AK60" t="s" s="2">
+      <c r="AL60" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="AL60" t="s" s="2">
+      <c r="AM60" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>77</v>
@@ -8849,10 +8837,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8875,19 +8863,19 @@
         <v>77</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="N61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>77</v>
@@ -8936,7 +8924,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8951,13 +8939,13 @@
         <v>99</v>
       </c>
       <c r="AK61" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AL61" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="AL61" t="s" s="2">
+      <c r="AM61" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>77</v>
@@ -8965,10 +8953,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8991,19 +8979,19 @@
         <v>77</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="O62" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>77</v>
@@ -9052,7 +9040,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9064,13 +9052,13 @@
         <v>149</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>272</v>
+        <v>449</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>77</v>
